--- a/build/sources/Promotions.xlsx
+++ b/build/sources/Promotions.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Promotions'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Promotions'!$A$1:$L$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,8 +33,16 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="0038761D"/>
+    </font>
+    <font>
       <color rgb="000563C1"/>
       <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00999999"/>
     </font>
     <font>
       <b val="1"/>
@@ -48,7 +56,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -62,12 +70,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,29 +115,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="general" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="general" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -485,19 +509,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,25 +554,35 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Date of Event</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Promotion Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Asset Link</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Asset Status</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Include on Promotions Page?</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -578,25 +614,39 @@
           <t>Horse Racing</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>13 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Multi Bet &amp; Get (Bet 10 Get 5): Horse Racing</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>No Asset</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+          <t>Open asset</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>Multi bet &amp; get; no link supplied</t>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Daily racing multi bet &amp; get</t>
         </is>
       </c>
     </row>
@@ -626,25 +676,39 @@
           <t>The Open</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>The Open - 12 Places</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>No Asset</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+          <t>Open asset</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Golf major (The Open Championship); enhanced 12 places</t>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Golf major; repeat outright promo, event-day copy included instead</t>
         </is>
       </c>
     </row>
@@ -674,27 +738,37 @@
           <t>France v Spain</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>50% Bet Builder Boost: France v Spain</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Open BBB file</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>World Cup semi-final; local BBB asset</t>
         </is>
@@ -726,27 +800,37 @@
           <t>France v Spain</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bet 10 Get 5 Squad Builder: France v Spain</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Open asset</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>World Cup semi-final; football matches design folder</t>
         </is>
@@ -778,25 +862,39 @@
           <t>The Open</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>The Open - 12 Places</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>No Asset</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+          <t>Open asset</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Golf major; enhanced 12 places</t>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Golf major; repeat outright promo</t>
         </is>
       </c>
     </row>
@@ -826,25 +924,35 @@
           <t>The Open</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Outright Boost: The Open</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Golf major; outright market boost</t>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Golf major; repeat outright promo</t>
         </is>
       </c>
     </row>
@@ -874,27 +982,37 @@
           <t>Argentina v England</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>15 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Super Boost: Argentina v England</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Open asset</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>World Cup semi-final; football Super Boost creative</t>
         </is>
@@ -926,27 +1044,37 @@
           <t>Argentina v England</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>15 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Bet 5 Get 5 + 5 if Qualify: Argentina v England</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Open asset</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>World Cup semi-final; football matches design folder</t>
         </is>
@@ -978,25 +1106,39 @@
           <t>The Open</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>The Open - 12 Places</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>No Asset</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+          <t>Open asset</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Golf major; enhanced 12 places</t>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Golf major; event-day copy for the outright/places promo</t>
         </is>
       </c>
     </row>
@@ -1026,25 +1168,35 @@
           <t>The Open</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Outright Boost: The Open</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Golf major; outright market boost</t>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Golf major; event-day copy for the outright boost</t>
         </is>
       </c>
     </row>
@@ -1074,25 +1226,35 @@
           <t>The Open</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Price Boost: The Open</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Golf major; price boost</t>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Golf major; daily price boost (Rd 1); golf price boosts excluded from promotions page</t>
         </is>
       </c>
     </row>
@@ -1122,23 +1284,33 @@
           <t>World Matchplay</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Outright PPB: World Matchplay</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Darts (Betfred World Matchplay); outright price-promise boost</t>
         </is>
@@ -1170,25 +1342,39 @@
           <t>Horse Racing</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>16 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Multi Bet &amp; Get (Bet 10 Get 5): Horse Racing</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>No Asset</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+          <t>Open asset</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Multi bet &amp; get; no link supplied</t>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Daily racing multi bet &amp; get</t>
         </is>
       </c>
     </row>
@@ -1218,25 +1404,35 @@
           <t>The Open</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Bet 10 Get 5: The Open</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>Golf major; non-football bet &amp; get, no link supplied</t>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Golf major; non-football bet &amp; get</t>
         </is>
       </c>
     </row>
@@ -1266,25 +1462,35 @@
           <t>The Open</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Price Boost: The Open</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Golf major; price boost</t>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Golf major; daily price boost (Rd 2); golf price boosts excluded from promotions page</t>
         </is>
       </c>
     </row>
@@ -1314,25 +1520,35 @@
           <t>3rd Place Play-Off</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>50% Bet Builder Boost: 3rd Place Play-Off</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>World Cup 3rd place play-off; teams TBC</t>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>World Cup 3rd place play-off (18 Jul); pre-event repeat</t>
         </is>
       </c>
     </row>
@@ -1362,25 +1578,39 @@
           <t>Horse Racing</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>17 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>Multi Bet &amp; Get (Bet 10 Get 5): Horse Racing</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>No Asset</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+          <t>Open asset</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>Multi bet &amp; get; no link supplied</t>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Daily racing multi bet &amp; get</t>
         </is>
       </c>
     </row>
@@ -1410,23 +1640,33 @@
           <t>Horse Racing</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Best Odds Guaranteed: Horse Racing</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>Best Odds Guaranteed</t>
         </is>
@@ -1458,25 +1698,35 @@
           <t>All-Ireland Hurling Final</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>Super Boost: All-Ireland Hurling Final</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>GAA major; non-football Super Boost, no link</t>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>GAA major (19 Jul); pre-event repeat; non-football Super Boost</t>
         </is>
       </c>
     </row>
@@ -1506,25 +1756,35 @@
           <t>The Open</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Price Boost: The Open</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Golf major; price boost</t>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Golf major; daily price boost (Rd 3); golf price boosts excluded from promotions page</t>
         </is>
       </c>
     </row>
@@ -1554,25 +1814,35 @@
           <t>3rd Place Play-Off</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>50% Bet Builder Boost: 3rd Place Play-Off</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>World Cup 3rd place play-off; teams TBC</t>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>World Cup 3rd place play-off; event day; teams TBC</t>
         </is>
       </c>
     </row>
@@ -1602,29 +1872,39 @@
           <t>World Cup Final</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Super Boost: World Cup Final</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Open asset</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>World Cup Final; football Super Boost creative; teams TBC</t>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>World Cup Final (19 Jul); pre-event repeat; teams TBC</t>
         </is>
       </c>
     </row>
@@ -1654,23 +1934,33 @@
           <t>World Matchplay</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Bet &amp; Get: World Matchplay</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>Darts (World Matchplay); non-football bet &amp; get</t>
         </is>
@@ -1702,23 +1992,33 @@
           <t>World Matchplay</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>18 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>EPO: World Matchplay</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>Darts (World Matchplay)</t>
         </is>
@@ -1750,23 +2050,33 @@
           <t>Horse Racing</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Best Odds Guaranteed: Horse Racing</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>Best Odds Guaranteed</t>
         </is>
@@ -1798,25 +2108,35 @@
           <t>All-Ireland Hurling Final</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Super Boost: All-Ireland Hurling Final</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>GAA major; non-football Super Boost, no link</t>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>GAA major; event day; non-football Super Boost, no link</t>
         </is>
       </c>
     </row>
@@ -1846,29 +2166,39 @@
           <t>World Cup Final</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>Super Boost: World Cup Final</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Open asset</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>World Cup Final; football Super Boost creative; teams TBC</t>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>World Cup Final; event day; football Super Boost creative; teams TBC</t>
         </is>
       </c>
     </row>
@@ -1898,25 +2228,35 @@
           <t>The Open</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Price Boost: The Open</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>Golf major; price boost</t>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Golf major; daily price boost (Final Rd); golf price boosts excluded from promotions page</t>
         </is>
       </c>
     </row>
@@ -1946,23 +2286,33 @@
           <t>World Matchplay</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Bet &amp; Get: World Matchplay</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr">
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>Darts (World Matchplay); non-football bet &amp; get</t>
         </is>
@@ -1994,37 +2344,53 @@
           <t>World Matchplay</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>19 Jul 2026</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>EPO: World Matchplay</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>No Asset</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>Darts (World Matchplay)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:L31"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2036,88 +2402,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>WEEKLY PROMOTIONS SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>13 – 19 Jul 2026</t>
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>13 - 19 Jul 2026</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Total Promotions</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="11" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Promotions by Day</t>
-        </is>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>On Promotions Page (Y)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Excluded (N)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Promotions by Day</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -2127,277 +2483,225 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Promotions by Sport</t>
-        </is>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Football</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Horse Racing</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>5</v>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Promotions by Sport</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Darts</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gaelic Games</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Horse Racing</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Promotions by Type</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Darts</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bet &amp; Get</t>
+          <t>Gaelic Games</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Super Boost</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Price Boost</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4</v>
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Promotions by Type</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Boost / Places</t>
+          <t>Bet &amp; Get</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>50% BBB</t>
+          <t>Super Boost</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Outright Boost</t>
+          <t>Price Boost</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BOG</t>
+          <t>Boost / Places</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EPO</t>
+          <t>50% BBB</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PPB</t>
+          <t>Outright Boost</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BOG</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Promotions Missing Assets</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n">
-        <v>24</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EPO</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>PPB</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>High Priority Promotions</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="n">
-        <v>6</v>
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Available Assets</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wed 15 Jul 2026</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Super Boost: Argentina v England</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Wed 15 Jul 2026</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Bet 5 Get 5 + 5 if Qualify: Argentina v England</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Sat 18 Jul 2026</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Super Boost: All-Ireland Hurling Final</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Sat 18 Jul 2026</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Super Boost: World Cup Final</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Sun 19 Jul 2026</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Super Boost: All-Ireland Hurling Final</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Sun 19 Jul 2026</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Super Boost: World Cup Final</t>
-        </is>
+          <t>No Asset</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
